--- a/docentes/Loyo Sanchez Raul Manuel - Estadisticos 20221.xlsx
+++ b/docentes/Loyo Sanchez Raul Manuel - Estadisticos 20221.xlsx
@@ -548,16 +548,19 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>36</v>
       </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
-        <v>0</v>
+        <v>87.8</v>
+      </c>
+      <c r="H2">
+        <v>8.300000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -622,7 +625,7 @@
         <v>87.8</v>
       </c>
       <c r="H2">
-        <v>8.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Loyo Sanchez Raul Manuel - Estadisticos 20221.xlsx
+++ b/docentes/Loyo Sanchez Raul Manuel - Estadisticos 20221.xlsx
@@ -67,22 +67,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
     <t>ARELLANO</t>
   </si>
   <si>
-    <t>BONILLA</t>
+    <t>IBAÑEZ</t>
   </si>
   <si>
     <t>FIERROS</t>
   </si>
   <si>
-    <t>IBAÑEZ</t>
+    <t>FERNANDA MARGARITA</t>
   </si>
   <si>
     <t>ALDO EMANUEL</t>
-  </si>
-  <si>
-    <t>FERNANDA MARGARITA</t>
   </si>
 </sst>
 </file>
@@ -667,7 +667,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920231</v>
+        <v>22330051920233</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
@@ -685,12 +685,12 @@
         <v>9</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920233</v>
+        <v>22330051920231</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>

--- a/docentes/Loyo Sanchez Raul Manuel - Estadisticos 20221.xlsx
+++ b/docentes/Loyo Sanchez Raul Manuel - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="19">
   <si>
     <t>Mat</t>
   </si>
@@ -67,19 +67,10 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>BONILLA</t>
-  </si>
-  <si>
     <t>ARELLANO</t>
   </si>
   <si>
-    <t>IBAÑEZ</t>
-  </si>
-  <si>
     <t>FIERROS</t>
-  </si>
-  <si>
-    <t>FERNANDA MARGARITA</t>
   </si>
   <si>
     <t>ALDO EMANUEL</t>
@@ -635,7 +626,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -667,16 +658,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920233</v>
+        <v>22330051920231</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
       </c>
       <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
         <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>20</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -685,29 +676,6 @@
         <v>9</v>
       </c>
       <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>22330051920231</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Loyo Sanchez Raul Manuel - Estadisticos 20221.xlsx
+++ b/docentes/Loyo Sanchez Raul Manuel - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="16">
   <si>
     <t>Mat</t>
   </si>
@@ -65,15 +65,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>FIERROS</t>
-  </si>
-  <si>
-    <t>ALDO EMANUEL</t>
   </si>
 </sst>
 </file>
@@ -474,19 +465,19 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G2">
-        <v>87.8</v>
+        <v>95.12</v>
       </c>
       <c r="H2">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
     </row>
   </sheetData>
@@ -539,19 +530,19 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G2">
-        <v>87.8</v>
+        <v>95.12</v>
       </c>
       <c r="H2">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
     </row>
   </sheetData>
@@ -604,19 +595,19 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G2">
-        <v>87.8</v>
+        <v>95.12</v>
       </c>
       <c r="H2">
-        <v>9.199999999999999</v>
+        <v>8.9</v>
       </c>
     </row>
   </sheetData>
@@ -626,7 +617,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -656,29 +647,6 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>22330051920231</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
